--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D03F56-CDEE-4553-B6BB-9828A79B749D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>48984</t>
   </si>
@@ -64,12 +70,12 @@
     <t>436512</t>
   </si>
   <si>
+    <t>571937</t>
+  </si>
+  <si>
     <t>436503</t>
   </si>
   <si>
-    <t>571937</t>
-  </si>
-  <si>
     <t>436513</t>
   </si>
   <si>
@@ -85,9 +91,6 @@
     <t>436510</t>
   </si>
   <si>
-    <t>436505</t>
-  </si>
-  <si>
     <t>436509</t>
   </si>
   <si>
@@ -109,12 +112,12 @@
     <t>Denominación de cada informe</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Descripción de la temática que se aborda en el informe</t>
+  </si>
+  <si>
     <t>Denominación del área responsable de la elaboración y/o presentación del informe</t>
   </si>
   <si>
-    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Descripción de la temática que se aborda en el informe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fundamento legal </t>
   </si>
   <si>
@@ -130,55 +133,55 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>5B590292DD767EAD264F6D1C4B046186</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>Informes de actividades</t>
-  </si>
-  <si>
-    <t>Área de Transparencia</t>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Informe de actividades</t>
+  </si>
+  <si>
+    <t>Unidad de Transparencia</t>
+  </si>
+  <si>
+    <t>Ley General de Transparencia</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>27/12/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/Informe%202022%20transparencia%20y%20archivo.pdf</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Ley de General de Transparencia, Ley de Transparencia del Estado de Tlaxcala, Ley General de Archivos y Ley de Archivos del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Anual</t>
-  </si>
-  <si>
-    <t>Área de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>17/04/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril del 2023, al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no ha generado informes, lo anterior por motivo de que estos son efectuados de forma anual mismo que generaliza todas las actividades efectuadas durante el ejercicio, las cuales son planeadas mediante el Plan Anual de Trabajo.</t>
+    <t>EE615424E86393635B362BD4B7EFEE82</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>El informe precisa actividades de acuerdo al Plan Anual de Trabajo, que se emplea de acuerdo a las funciones y/o atribuciones de la Unidad de Transparencia</t>
+  </si>
+  <si>
+    <t>02/07/2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -274,6 +277,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -289,44 +295,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -354,14 +360,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -389,6 +412,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -400,197 +440,172 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="123" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="133.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="128.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -607,7 +622,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -622,7 +637,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -657,16 +672,13 @@
         <v>8</v>
       </c>
       <c r="M4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -706,13 +718,10 @@
       <c r="N5" t="s">
         <v>24</v>
       </c>
-      <c r="O5" t="s">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -727,102 +736,95 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D03F56-CDEE-4553-B6BB-9828A79B749D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82234338-8B05-4A0A-94FA-09F6F5FAC58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,12 +139,24 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>1EFAB4C00D86CBFD759E0F25E3E7D370</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Informe de actividades</t>
   </si>
   <si>
+    <t>El informe precisa actividades de acuerdo al Plan Anual de Trabajo, que se emplea de acuerdo a las funciones y/o atribuciones de la Unidad  de Transparencia</t>
+  </si>
+  <si>
     <t>Unidad de Transparencia</t>
   </si>
   <si>
@@ -160,22 +172,10 @@
     <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/Informe%202022%20transparencia%20y%20archivo.pdf</t>
   </si>
   <si>
+    <t>09/09/2024</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>EE615424E86393635B362BD4B7EFEE82</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>El informe precisa actividades de acuerdo al Plan Anual de Trabajo, que se emplea de acuerdo a las funciones y/o atribuciones de la Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
   </si>
 </sst>
 </file>
@@ -780,46 +780,46 @@
     </row>
     <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
